--- a/results/ai_run/543_z13/5_quantification/543_z13_quantification.xlsx
+++ b/results/ai_run/543_z13/5_quantification/543_z13_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13.0909</v>
+        <v>9.545500000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>3.7538</v>
+        <v>2.6216</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6.4973</v>
+        <v>4.6785</v>
       </c>
       <c r="D25" t="n">
-        <v>5.8526</v>
+        <v>4.2451</v>
       </c>
       <c r="E25" t="n">
-        <v>2.0099</v>
+        <v>1.1799</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
@@ -2592,7 +2592,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M2" t="n">
         <v>357</v>
@@ -2631,7 +2631,7 @@
         <v>0.04327563</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.8526</v>
+        <v>3.9017</v>
       </c>
       <c r="Z2" t="n">
         <v>355</v>
@@ -2699,7 +2699,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="M3" t="n">
         <v>422</v>
@@ -2738,7 +2738,7 @@
         <v>0.05822556</v>
       </c>
       <c r="Y3" t="n">
-        <v>11.2362</v>
+        <v>7.2705</v>
       </c>
       <c r="Z3" t="n">
         <v>397</v>
@@ -2806,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M4" t="n">
         <v>408</v>
@@ -2845,7 +2845,7 @@
         <v>0.04839112</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.8035</v>
+        <v>5.3649</v>
       </c>
       <c r="Z4" t="n">
         <v>334</v>
@@ -2913,7 +2913,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
         <v>305</v>
@@ -2952,7 +2952,7 @@
         <v>0.05016053</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.0114</v>
+        <v>3.5796</v>
       </c>
       <c r="Z5" t="n">
         <v>300</v>
@@ -3020,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M6" t="n">
         <v>418</v>
@@ -3059,7 +3059,7 @@
         <v>0.04924743</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.3614</v>
+        <v>4.9146</v>
       </c>
       <c r="Z6" t="n">
         <v>374</v>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
         <v>415</v>
@@ -3166,7 +3166,7 @@
         <v>0.05691194</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.6602</v>
+        <v>4.2451</v>
       </c>
       <c r="Z7" t="n">
         <v>370</v>
@@ -3234,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="M8" t="n">
         <v>525</v>
@@ -3273,7 +3273,7 @@
         <v>0.05150127</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.8451</v>
+        <v>5.0993</v>
       </c>
       <c r="Z8" t="n">
         <v>525</v>
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M9" t="n">
         <v>519</v>
@@ -3380,7 +3380,7 @@
         <v>0.04537363</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.0253</v>
+        <v>3.5895</v>
       </c>
       <c r="Z9" t="n">
         <v>505</v>
@@ -3448,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
         <v>337</v>
@@ -3487,7 +3487,7 @@
         <v>0.03890979</v>
       </c>
       <c r="Y10" t="n">
-        <v>6.1311</v>
+        <v>3.5765</v>
       </c>
       <c r="Z10" t="n">
         <v>297</v>
@@ -3555,7 +3555,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M11" t="n">
         <v>429</v>
@@ -3594,7 +3594,7 @@
         <v>0.05012908</v>
       </c>
       <c r="Y11" t="n">
-        <v>7.5678</v>
+        <v>5.9461</v>
       </c>
       <c r="Z11" t="n">
         <v>393</v>
